--- a/VMS.xlsx
+++ b/VMS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\training\NiceDevOps\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\training\NiceDevOps\repository\NiceDevOpsTraining\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC5AE31-33EE-4502-8821-3AE6A83FEC95}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9DBF87-7062-4E9C-81A0-2C6077913879}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="101">
   <si>
     <t>Username</t>
   </si>
@@ -268,6 +268,66 @@
   </si>
   <si>
     <t>Trainer</t>
+  </si>
+  <si>
+    <t>Malvika</t>
+  </si>
+  <si>
+    <t>Anushka</t>
+  </si>
+  <si>
+    <t>Ritesh</t>
+  </si>
+  <si>
+    <t>Shashank</t>
+  </si>
+  <si>
+    <t>Aditya</t>
+  </si>
+  <si>
+    <t>Neha</t>
+  </si>
+  <si>
+    <t>Aditi</t>
+  </si>
+  <si>
+    <t>Annie</t>
+  </si>
+  <si>
+    <t>Kunal</t>
+  </si>
+  <si>
+    <t>Aman</t>
+  </si>
+  <si>
+    <t>Purva</t>
+  </si>
+  <si>
+    <t>Siya</t>
+  </si>
+  <si>
+    <t>Aishwarya</t>
+  </si>
+  <si>
+    <t>Prajwal</t>
+  </si>
+  <si>
+    <t>Pranav</t>
+  </si>
+  <si>
+    <t>Ajinkya</t>
+  </si>
+  <si>
+    <t>Mahemud</t>
+  </si>
+  <si>
+    <t>Abhishek</t>
+  </si>
+  <si>
+    <t>50175user19</t>
+  </si>
+  <si>
+    <t>50175user4u#19</t>
   </si>
 </sst>
 </file>
@@ -365,7 +425,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -490,12 +550,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -538,20 +609,40 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -835,11 +926,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C2:K22"/>
+  <dimension ref="C2:K23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="6.81640625" customWidth="1"/>
-    <col min="4" max="4" width="34.26953125" customWidth="1"/>
+    <col min="4" max="4" width="34.90625" customWidth="1"/>
     <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.90625" customWidth="1"/>
     <col min="7" max="11" width="0" hidden="1" customWidth="1"/>
@@ -860,16 +951,16 @@
       <c r="F3" s="11"/>
     </row>
     <row r="4" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="16" t="s">
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -892,7 +983,9 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="14"/>
+      <c r="D5" s="20" t="s">
+        <v>81</v>
+      </c>
       <c r="E5" s="15" t="s">
         <v>10</v>
       </c>
@@ -909,13 +1002,15 @@
       <c r="J5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="19"/>
+      <c r="K5" s="17"/>
     </row>
     <row r="6" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C6" s="14">
         <v>2</v>
       </c>
-      <c r="D6" s="14"/>
+      <c r="D6" s="20" t="s">
+        <v>82</v>
+      </c>
       <c r="E6" s="15" t="s">
         <v>14</v>
       </c>
@@ -932,13 +1027,15 @@
       <c r="J6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K6" s="19"/>
+      <c r="K6" s="17"/>
     </row>
     <row r="7" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C7" s="14">
         <v>3</v>
       </c>
-      <c r="D7" s="14"/>
+      <c r="D7" s="20" t="s">
+        <v>83</v>
+      </c>
       <c r="E7" s="15" t="s">
         <v>18</v>
       </c>
@@ -955,13 +1052,15 @@
       <c r="J7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="19"/>
+      <c r="K7" s="17"/>
     </row>
     <row r="8" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C8" s="14">
         <v>4</v>
       </c>
-      <c r="D8" s="14"/>
+      <c r="D8" s="20" t="s">
+        <v>84</v>
+      </c>
       <c r="E8" s="15" t="s">
         <v>22</v>
       </c>
@@ -978,13 +1077,15 @@
       <c r="J8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="19"/>
+      <c r="K8" s="17"/>
     </row>
     <row r="9" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C9" s="14">
         <v>5</v>
       </c>
-      <c r="D9" s="14"/>
+      <c r="D9" s="20" t="s">
+        <v>85</v>
+      </c>
       <c r="E9" s="15" t="s">
         <v>26</v>
       </c>
@@ -1001,13 +1102,15 @@
       <c r="J9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K9" s="19"/>
+      <c r="K9" s="17"/>
     </row>
     <row r="10" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C10" s="14">
         <v>6</v>
       </c>
-      <c r="D10" s="14"/>
+      <c r="D10" s="20" t="s">
+        <v>86</v>
+      </c>
       <c r="E10" s="15" t="s">
         <v>30</v>
       </c>
@@ -1024,13 +1127,15 @@
       <c r="J10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="K10" s="19"/>
+      <c r="K10" s="17"/>
     </row>
     <row r="11" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C11" s="14">
         <v>7</v>
       </c>
-      <c r="D11" s="14"/>
+      <c r="D11" s="20" t="s">
+        <v>87</v>
+      </c>
       <c r="E11" s="15" t="s">
         <v>34</v>
       </c>
@@ -1047,13 +1152,15 @@
       <c r="J11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K11" s="19"/>
+      <c r="K11" s="17"/>
     </row>
     <row r="12" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C12" s="14">
         <v>8</v>
       </c>
-      <c r="D12" s="14"/>
+      <c r="D12" s="20" t="s">
+        <v>88</v>
+      </c>
       <c r="E12" s="15" t="s">
         <v>38</v>
       </c>
@@ -1070,13 +1177,15 @@
       <c r="J12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K12" s="19"/>
+      <c r="K12" s="17"/>
     </row>
     <row r="13" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C13" s="14">
         <v>9</v>
       </c>
-      <c r="D13" s="14"/>
+      <c r="D13" s="20" t="s">
+        <v>89</v>
+      </c>
       <c r="E13" s="15" t="s">
         <v>42</v>
       </c>
@@ -1093,13 +1202,15 @@
       <c r="J13" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="K13" s="19"/>
+      <c r="K13" s="17"/>
     </row>
     <row r="14" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C14" s="14">
         <v>10</v>
       </c>
-      <c r="D14" s="14"/>
+      <c r="D14" s="20" t="s">
+        <v>90</v>
+      </c>
       <c r="E14" s="15" t="s">
         <v>46</v>
       </c>
@@ -1116,13 +1227,15 @@
       <c r="J14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="K14" s="19"/>
+      <c r="K14" s="17"/>
     </row>
     <row r="15" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C15" s="14">
         <v>11</v>
       </c>
-      <c r="D15" s="14"/>
+      <c r="D15" s="20" t="s">
+        <v>91</v>
+      </c>
       <c r="E15" s="15" t="s">
         <v>50</v>
       </c>
@@ -1139,13 +1252,15 @@
       <c r="J15" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="19"/>
+      <c r="K15" s="17"/>
     </row>
     <row r="16" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C16" s="14">
         <v>12</v>
       </c>
-      <c r="D16" s="14"/>
+      <c r="D16" s="20" t="s">
+        <v>92</v>
+      </c>
       <c r="E16" s="15" t="s">
         <v>54</v>
       </c>
@@ -1162,13 +1277,15 @@
       <c r="J16" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="20"/>
+      <c r="K16" s="18"/>
     </row>
     <row r="17" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C17" s="14">
         <v>13</v>
       </c>
-      <c r="D17" s="14"/>
+      <c r="D17" s="20" t="s">
+        <v>93</v>
+      </c>
       <c r="E17" s="15" t="s">
         <v>58</v>
       </c>
@@ -1185,7 +1302,7 @@
       <c r="J17" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="21">
+      <c r="K17" s="19">
         <v>173</v>
       </c>
     </row>
@@ -1193,7 +1310,9 @@
       <c r="C18" s="14">
         <v>14</v>
       </c>
-      <c r="D18" s="14"/>
+      <c r="D18" s="20" t="s">
+        <v>94</v>
+      </c>
       <c r="E18" s="15" t="s">
         <v>62</v>
       </c>
@@ -1210,13 +1329,15 @@
       <c r="J18" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K18" s="19"/>
+      <c r="K18" s="17"/>
     </row>
     <row r="19" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C19" s="14">
         <v>15</v>
       </c>
-      <c r="D19" s="14"/>
+      <c r="D19" s="20" t="s">
+        <v>95</v>
+      </c>
       <c r="E19" s="15" t="s">
         <v>66</v>
       </c>
@@ -1233,13 +1354,15 @@
       <c r="J19" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="K19" s="19"/>
+      <c r="K19" s="17"/>
     </row>
     <row r="20" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C20" s="14">
         <v>16</v>
       </c>
-      <c r="D20" s="14"/>
+      <c r="D20" s="20" t="s">
+        <v>96</v>
+      </c>
       <c r="E20" s="15" t="s">
         <v>70</v>
       </c>
@@ -1256,13 +1379,15 @@
       <c r="J20" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K20" s="19"/>
+      <c r="K20" s="17"/>
     </row>
     <row r="21" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C21" s="14">
         <v>17</v>
       </c>
-      <c r="D21" s="16"/>
+      <c r="D21" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="E21" s="15" t="s">
         <v>74</v>
       </c>
@@ -1279,19 +1404,38 @@
       <c r="J21" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="K21" s="20"/>
+      <c r="K21" s="18"/>
     </row>
     <row r="22" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C22" s="14">
         <v>18</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G22" s="24"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="27"/>
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C23" s="14">
+        <v>19</v>
+      </c>
+      <c r="D23" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E23" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F23" s="15" t="s">
         <v>9</v>
       </c>
     </row>
